--- a/data/Data Ketenagakerjaan.xlsx
+++ b/data/Data Ketenagakerjaan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\jaktimstats_flutter\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\jaktimstats-data-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11046001-36B9-4072-9722-11755AB95975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B852B220-42FD-409E-963C-C0F3421538E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEF38B52-B14D-4179-9B51-FECABD6B0A0D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>DATA STRATEGIS KOTA JAKARTA TIMUR 2010 - 2025</t>
   </si>
@@ -54,94 +54,10 @@
     <t>Persen</t>
   </si>
   <si>
-    <t>10.95</t>
-  </si>
-  <si>
-    <t>10.39</t>
-  </si>
-  <si>
-    <t>8.99</t>
-  </si>
-  <si>
-    <t>8.72</t>
-  </si>
-  <si>
-    <t>9.13</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>7.80</t>
-  </si>
-  <si>
-    <t>7.13</t>
-  </si>
-  <si>
-    <t>6.35</t>
-  </si>
-  <si>
-    <t>9.29</t>
-  </si>
-  <si>
-    <t>8.23</t>
-  </si>
-  <si>
-    <t>8.39</t>
-  </si>
-  <si>
-    <t>7.24</t>
-  </si>
-  <si>
-    <t>6.95</t>
-  </si>
-  <si>
     <t>Tingkat Partisipasi Angkatan Kerja (TPAK)</t>
-  </si>
-  <si>
-    <t>65.13</t>
-  </si>
-  <si>
-    <t>69.85</t>
-  </si>
-  <si>
-    <t>64.57</t>
-  </si>
-  <si>
-    <t>64.90</t>
-  </si>
-  <si>
-    <t>64.83</t>
-  </si>
-  <si>
-    <t>64.55</t>
-  </si>
-  <si>
-    <t>58.90</t>
-  </si>
-  <si>
-    <t>61.77</t>
-  </si>
-  <si>
-    <t>64.88</t>
-  </si>
-  <si>
-    <t>61.98</t>
-  </si>
-  <si>
-    <t>60.85</t>
-  </si>
-  <si>
-    <t>61.26</t>
-  </si>
-  <si>
-    <t>65.11</t>
-  </si>
-  <si>
-    <t>64.49</t>
-  </si>
-  <si>
-    <t>64.00</t>
   </si>
   <si>
     <t>Penduduk Usia Kerja (PUK)</t>
@@ -150,70 +66,16 @@
     <t>Orang</t>
   </si>
   <si>
-    <t>2,265,063</t>
-  </si>
-  <si>
-    <t>2,387,325</t>
-  </si>
-  <si>
-    <t>2,401,367</t>
-  </si>
-  <si>
     <t>Angkatan Kerja</t>
   </si>
   <si>
-    <t>1,387,533</t>
-  </si>
-  <si>
-    <t>1,554,276</t>
-  </si>
-  <si>
-    <t>1,548,679</t>
-  </si>
-  <si>
     <t>- Bekerja</t>
-  </si>
-  <si>
-    <t>1,271,123</t>
-  </si>
-  <si>
-    <t>1,441,786</t>
-  </si>
-  <si>
-    <t>1,441,119</t>
-  </si>
-  <si>
-    <t>1,446,879</t>
   </si>
   <si>
     <t>- Pengangguran</t>
   </si>
   <si>
     <t>Bukan Angkatan Kerja</t>
-  </si>
-  <si>
-    <t>2,236,887</t>
-  </si>
-  <si>
-    <t>2,251,875</t>
-  </si>
-  <si>
-    <t>2,424,998</t>
-  </si>
-  <si>
-    <t>2,386,492</t>
-  </si>
-  <si>
-    <t>1,370,294</t>
-  </si>
-  <si>
-    <t>1,552,037</t>
-  </si>
-  <si>
-    <t>2,257,752</t>
-  </si>
-  <si>
-    <t>1,257,540</t>
   </si>
 </sst>
 </file>
@@ -306,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -333,17 +195,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -358,6 +214,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -678,27 +555,27 @@
     <col min="2" max="2" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -936,352 +813,352 @@
       <c r="C7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="12">
-        <v>45729</v>
-      </c>
-      <c r="E7" s="13" t="s">
+      <c r="D7" s="20">
+        <v>13.3</v>
+      </c>
+      <c r="E7" s="20">
+        <v>10.95</v>
+      </c>
+      <c r="F7" s="20">
+        <v>10.39</v>
+      </c>
+      <c r="G7" s="20">
+        <v>8.99</v>
+      </c>
+      <c r="H7" s="20">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="I7" s="20">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="J7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="P7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="R7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="S7" s="13">
+      <c r="K7" s="20">
+        <v>7.8</v>
+      </c>
+      <c r="L7" s="20">
+        <v>7.13</v>
+      </c>
+      <c r="M7" s="20">
+        <v>6.35</v>
+      </c>
+      <c r="N7" s="20">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="O7" s="20">
+        <v>8.23</v>
+      </c>
+      <c r="P7" s="20">
+        <v>8.39</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>7.24</v>
+      </c>
+      <c r="R7" s="20">
+        <v>6.95</v>
+      </c>
+      <c r="S7" s="20">
         <v>6.78</v>
       </c>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="11" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="13" t="s">
+      <c r="D8" s="20">
+        <v>65.13</v>
+      </c>
+      <c r="E8" s="20">
+        <v>69.849999999999994</v>
+      </c>
+      <c r="F8" s="20">
+        <v>64.569999999999993</v>
+      </c>
+      <c r="G8" s="20">
+        <v>64.900000000000006</v>
+      </c>
+      <c r="H8" s="20">
+        <v>64.83</v>
+      </c>
+      <c r="I8" s="20">
+        <v>64.55</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="20">
+        <v>58.9</v>
+      </c>
+      <c r="L8" s="20">
+        <v>61.77</v>
+      </c>
+      <c r="M8" s="20">
+        <v>64.88</v>
+      </c>
+      <c r="N8" s="20">
+        <v>61.98</v>
+      </c>
+      <c r="O8" s="20">
+        <v>60.85</v>
+      </c>
+      <c r="P8" s="20">
+        <v>61.26</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>65.11</v>
+      </c>
+      <c r="R8" s="20">
+        <v>64.489999999999995</v>
+      </c>
+      <c r="S8" s="21">
+        <v>64</v>
+      </c>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+    </row>
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="22">
+        <v>2236887</v>
+      </c>
+      <c r="O9" s="22">
+        <v>2251875</v>
+      </c>
+      <c r="P9" s="22">
+        <v>2265063</v>
+      </c>
+      <c r="Q9" s="22">
+        <v>2387325</v>
+      </c>
+      <c r="R9" s="22">
+        <v>2401367</v>
+      </c>
+      <c r="S9" s="23">
+        <v>2424998</v>
+      </c>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15"/>
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15"/>
+    </row>
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14"/>
+      <c r="B10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="22">
+        <v>2386492</v>
+      </c>
+      <c r="O10" s="22">
+        <v>1370294</v>
+      </c>
+      <c r="P10" s="22">
+        <v>1387533</v>
+      </c>
+      <c r="Q10" s="22">
+        <v>1554276</v>
+      </c>
+      <c r="R10" s="22">
+        <v>1548679</v>
+      </c>
+      <c r="S10" s="22">
+        <v>1552037</v>
+      </c>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+    </row>
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14"/>
+      <c r="B11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="P8" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q8" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="R8" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="S8" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-    </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
-      <c r="B9" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q9" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="R9" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="S9" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-    </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="O10" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="P10" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q10" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="R10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="S10" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-    </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
-      <c r="B11" s="10" t="s">
-        <v>45</v>
-      </c>
       <c r="C11" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q11" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="R11" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="S11" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="17"/>
+        <v>9</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="22">
+        <v>2257752</v>
+      </c>
+      <c r="O11" s="22">
+        <v>1257540</v>
+      </c>
+      <c r="P11" s="22">
+        <v>1271123</v>
+      </c>
+      <c r="Q11" s="22">
+        <v>1441786</v>
+      </c>
+      <c r="R11" s="22">
+        <v>1441119</v>
+      </c>
+      <c r="S11" s="23">
+        <v>1446879</v>
+      </c>
+      <c r="T11" s="15"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="15"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="15"/>
+      <c r="Z11" s="15"/>
+      <c r="AA11" s="15"/>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="10" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13">
-        <v>128.739</v>
-      </c>
-      <c r="O12" s="13">
-        <v>112.754</v>
-      </c>
-      <c r="P12" s="13">
-        <v>116.41</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>112.49</v>
-      </c>
-      <c r="R12" s="13">
-        <v>107.56</v>
-      </c>
-      <c r="S12" s="15">
-        <v>105.158</v>
-      </c>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
+        <v>9</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="24">
+        <v>128739</v>
+      </c>
+      <c r="O12" s="24">
+        <v>112754</v>
+      </c>
+      <c r="P12" s="24">
+        <v>116410</v>
+      </c>
+      <c r="Q12" s="24">
+        <v>112490</v>
+      </c>
+      <c r="R12" s="24">
+        <v>107560</v>
+      </c>
+      <c r="S12" s="25">
+        <v>105158</v>
+      </c>
+      <c r="T12" s="15"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="10" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13">
-        <v>850.39599999999996</v>
-      </c>
-      <c r="O13" s="13">
-        <v>881.58100000000002</v>
-      </c>
-      <c r="P13" s="13">
-        <v>877.53</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>833.04899999999998</v>
-      </c>
-      <c r="R13" s="13">
-        <v>852.68799999999999</v>
-      </c>
-      <c r="S13" s="13">
-        <v>872.96100000000001</v>
-      </c>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="17"/>
-      <c r="AA13" s="17"/>
+        <v>9</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="24">
+        <v>850396</v>
+      </c>
+      <c r="O13" s="24">
+        <v>881581</v>
+      </c>
+      <c r="P13" s="24">
+        <v>877530</v>
+      </c>
+      <c r="Q13" s="24">
+        <v>833049</v>
+      </c>
+      <c r="R13" s="24">
+        <v>852688</v>
+      </c>
+      <c r="S13" s="24">
+        <v>872961</v>
+      </c>
+      <c r="T13" s="15"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="15"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="15"/>
+      <c r="Y13" s="15"/>
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="15"/>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
@@ -1316,7 +1193,7 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="D15" s="18"/>
+      <c r="D15" s="16"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
